--- a/カードアクションキング/Data/Z/原本_スケジュール.xlsx
+++ b/カードアクションキング/Data/Z/原本_スケジュール.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\脇腹\Employment-work\カードアクションキング\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\脇腹\Employment-work\カードアクションキング\Data\Z\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55F1273C-D4BF-4196-B5B8-074AD28562CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8622EAE8-1D09-4B9E-A715-17B7552661E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5130" yWindow="3150" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{A0BA4298-C2C7-4C54-BB3A-0BA7CD3DD91A}"/>
+    <workbookView xWindow="1590" yWindow="3210" windowWidth="21600" windowHeight="11295" activeTab="5" xr2:uid="{A0BA4298-C2C7-4C54-BB3A-0BA7CD3DD91A}"/>
   </bookViews>
   <sheets>
     <sheet name="5月" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="50">
   <si>
     <t>5月</t>
     <rPh sb="1" eb="2">
@@ -217,6 +217,188 @@
     <t>カード処理</t>
     <rPh sb="3" eb="5">
       <t>ショリ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>AI（２P対応）</t>
+    <rPh sb="5" eb="7">
+      <t>タイオウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>UI</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>予定</t>
+    <rPh sb="0" eb="2">
+      <t>ヨテイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>現在</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンザイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>カード追加、デッキ構築</t>
+    <rPh sb="3" eb="5">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>コウチク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Battlescene調整</t>
+    <rPh sb="6" eb="13">
+      <t>シーンチョウセイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>へるぷ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>QA</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>学校</t>
+    <rPh sb="0" eb="2">
+      <t>ガッコウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>家</t>
+    <rPh sb="0" eb="1">
+      <t>イエ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>王の作成、カードマネージャーでCSVを2枚以上読み込み、</t>
+    <rPh sb="0" eb="1">
+      <t>オウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="20" eb="23">
+      <t>マイイジョウ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>現状進捗</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンジョウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シンチョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>細かい目安</t>
+    <rPh sb="0" eb="1">
+      <t>コマ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>メヤス</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>盤面作成</t>
+    <rPh sb="0" eb="2">
+      <t>バンメン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>読み込み</t>
+    <rPh sb="0" eb="1">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ユニット読み込み</t>
+    <rPh sb="4" eb="5">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ユニット1体</t>
+    <rPh sb="5" eb="6">
+      <t>タイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>量産</t>
+    <rPh sb="0" eb="2">
+      <t>リョウサン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>めも</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>現状進捗</t>
+    <rPh sb="0" eb="4">
+      <t>ゲンジョウシンチョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>UI調整</t>
+    <rPh sb="2" eb="4">
+      <t>チョウセイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>プレイの操作感</t>
+    <rPh sb="4" eb="7">
+      <t>ソウサカン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>へるぷ、吹き出し</t>
+    <rPh sb="4" eb="5">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ダ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -225,7 +407,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -273,8 +455,24 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -338,6 +536,42 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -412,7 +646,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -506,7 +740,70 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2301,37 +2598,41 @@
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.4">
-      <c r="A3" s="7"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="11"/>
-      <c r="S3" s="9"/>
-      <c r="T3" s="9"/>
-      <c r="U3" s="9"/>
-      <c r="V3" s="9"/>
-      <c r="W3" s="9"/>
-      <c r="X3" s="9"/>
-      <c r="Y3" s="9"/>
-      <c r="Z3" s="9"/>
-      <c r="AA3" s="9"/>
-      <c r="AB3" s="9"/>
-      <c r="AC3" s="9"/>
-      <c r="AD3" s="9"/>
-      <c r="AE3" s="9"/>
+      <c r="A3" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
+      <c r="M3" s="32"/>
+      <c r="N3" s="32"/>
+      <c r="O3" s="32"/>
+      <c r="P3" s="32"/>
+      <c r="Q3" s="32"/>
+      <c r="R3" s="33"/>
+      <c r="S3" s="32"/>
+      <c r="T3" s="32"/>
+      <c r="U3" s="32"/>
+      <c r="V3" s="32"/>
+      <c r="W3" s="32"/>
+      <c r="X3" s="32"/>
+      <c r="Y3" s="32"/>
+      <c r="Z3" s="32"/>
+      <c r="AA3" s="32"/>
+      <c r="AB3" s="32"/>
+      <c r="AC3" s="32"/>
+      <c r="AD3" s="32"/>
+      <c r="AE3" s="32"/>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A4" s="7"/>
@@ -2367,21 +2668,19 @@
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A5" s="7"/>
-      <c r="B5" s="31"/>
-      <c r="C5" s="31"/>
-      <c r="D5" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27"/>
-      <c r="I5" s="27"/>
-      <c r="J5" s="27"/>
-      <c r="K5" s="27"/>
-      <c r="L5" s="27"/>
-      <c r="M5" s="27"/>
-      <c r="N5" s="27"/>
+      <c r="B5" s="37"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="39"/>
+      <c r="J5" s="39"/>
+      <c r="K5" s="39"/>
+      <c r="L5" s="39"/>
+      <c r="M5" s="39"/>
+      <c r="N5" s="39"/>
       <c r="O5" s="9"/>
       <c r="P5" s="9"/>
       <c r="Q5" s="9"/>
@@ -2434,7 +2733,9 @@
       <c r="AE6" s="9"/>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.4">
-      <c r="A7" s="7"/>
+      <c r="A7" s="7" t="s">
+        <v>30</v>
+      </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
@@ -2457,7 +2758,9 @@
       <c r="U7" s="9"/>
       <c r="V7" s="9"/>
       <c r="W7" s="9"/>
-      <c r="X7" s="9"/>
+      <c r="X7" s="9" t="s">
+        <v>31</v>
+      </c>
       <c r="Y7" s="9"/>
       <c r="Z7" s="9"/>
       <c r="AA7" s="9"/>
@@ -2653,42 +2956,50 @@
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.4">
-      <c r="A3" s="7"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="11"/>
-      <c r="S3" s="9"/>
-      <c r="T3" s="9"/>
-      <c r="U3" s="9"/>
-      <c r="V3" s="9"/>
-      <c r="W3" s="9"/>
-      <c r="X3" s="9"/>
-      <c r="Y3" s="9"/>
-      <c r="Z3" s="9"/>
-      <c r="AA3" s="9"/>
-      <c r="AB3" s="9"/>
-      <c r="AC3" s="9"/>
-      <c r="AD3" s="9"/>
-      <c r="AE3" s="9"/>
-      <c r="AF3" s="9"/>
+      <c r="A3" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
+      <c r="L3" s="35"/>
+      <c r="M3" s="35"/>
+      <c r="N3" s="35"/>
+      <c r="O3" s="35"/>
+      <c r="P3" s="35"/>
+      <c r="Q3" s="35"/>
+      <c r="R3" s="36"/>
+      <c r="S3" s="35"/>
+      <c r="T3" s="35"/>
+      <c r="U3" s="35"/>
+      <c r="V3" s="35"/>
+      <c r="W3" s="35"/>
+      <c r="X3" s="35"/>
+      <c r="Y3" s="35"/>
+      <c r="Z3" s="35"/>
+      <c r="AA3" s="35"/>
+      <c r="AB3" s="35"/>
+      <c r="AC3" s="35"/>
+      <c r="AD3" s="35"/>
+      <c r="AE3" s="35"/>
+      <c r="AF3" s="35"/>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.4">
-      <c r="A4" s="7"/>
-      <c r="B4" s="8"/>
+      <c r="A4" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>37</v>
+      </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
@@ -2754,38 +3065,50 @@
       <c r="AF5" s="9"/>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.4">
-      <c r="A6" s="7"/>
+      <c r="A6" s="7" t="s">
+        <v>39</v>
+      </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
+      <c r="F6" s="47" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" s="47"/>
+      <c r="H6" s="47"/>
+      <c r="I6" s="48"/>
+      <c r="J6" s="48"/>
+      <c r="K6" s="48" t="s">
+        <v>41</v>
+      </c>
+      <c r="L6" s="48"/>
+      <c r="M6" s="48"/>
       <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
-      <c r="P6" s="9"/>
-      <c r="Q6" s="9"/>
-      <c r="R6" s="11"/>
-      <c r="S6" s="9"/>
-      <c r="T6" s="9"/>
-      <c r="U6" s="9"/>
-      <c r="V6" s="9"/>
-      <c r="W6" s="9"/>
-      <c r="X6" s="9"/>
-      <c r="Y6" s="9"/>
-      <c r="Z6" s="9"/>
-      <c r="AA6" s="9"/>
-      <c r="AB6" s="9"/>
-      <c r="AC6" s="9"/>
-      <c r="AD6" s="9"/>
-      <c r="AE6" s="9"/>
-      <c r="AF6" s="9"/>
+      <c r="O6" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="49" t="s">
+        <v>42</v>
+      </c>
+      <c r="S6" s="50"/>
+      <c r="T6" s="50"/>
+      <c r="U6" s="50"/>
+      <c r="V6" s="50"/>
+      <c r="W6" s="50"/>
+      <c r="X6" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y6" s="25"/>
+      <c r="Z6" s="25"/>
+      <c r="AA6" s="25"/>
+      <c r="AB6" s="25"/>
+      <c r="AC6" s="25"/>
+      <c r="AD6" s="25"/>
+      <c r="AE6" s="25"/>
+      <c r="AF6" s="25"/>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A7" s="7"/>
@@ -2822,7 +3145,9 @@
       <c r="AF7" s="9"/>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.4">
-      <c r="A8" s="7"/>
+      <c r="A8" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
@@ -3006,40 +3331,46 @@
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="A3" s="7"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="11"/>
-      <c r="S3" s="9"/>
-      <c r="T3" s="9"/>
-      <c r="U3" s="9"/>
-      <c r="V3" s="9"/>
-      <c r="W3" s="9"/>
-      <c r="X3" s="9"/>
-      <c r="Y3" s="9"/>
-      <c r="Z3" s="9"/>
-      <c r="AA3" s="9"/>
-      <c r="AB3" s="9"/>
-      <c r="AC3" s="9"/>
-      <c r="AD3" s="9"/>
-      <c r="AE3" s="9"/>
+      <c r="A3" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="41"/>
+      <c r="M3" s="41"/>
+      <c r="N3" s="41"/>
+      <c r="O3" s="41"/>
+      <c r="P3" s="41"/>
+      <c r="Q3" s="41"/>
+      <c r="R3" s="42"/>
+      <c r="S3" s="41"/>
+      <c r="T3" s="41"/>
+      <c r="U3" s="41"/>
+      <c r="V3" s="41"/>
+      <c r="W3" s="41"/>
+      <c r="X3" s="41"/>
+      <c r="Y3" s="41"/>
+      <c r="Z3" s="41"/>
+      <c r="AA3" s="41"/>
+      <c r="AB3" s="41"/>
+      <c r="AC3" s="41"/>
+      <c r="AD3" s="41"/>
+      <c r="AE3" s="41"/>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="A4" s="7"/>
+      <c r="A4" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -3054,7 +3385,9 @@
       <c r="M4" s="9"/>
       <c r="N4" s="9"/>
       <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
+      <c r="P4" s="9" t="s">
+        <v>33</v>
+      </c>
       <c r="Q4" s="9"/>
       <c r="S4" s="9"/>
       <c r="T4" s="9"/>
@@ -3104,6 +3437,364 @@
       <c r="AE5" s="9"/>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A6" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="51" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="52" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6" s="52"/>
+      <c r="H6" s="52"/>
+      <c r="I6" s="50"/>
+      <c r="J6" s="50"/>
+      <c r="K6" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="L6" s="25"/>
+      <c r="M6" s="25"/>
+      <c r="N6" s="25"/>
+      <c r="O6" s="25"/>
+      <c r="P6" s="25"/>
+      <c r="Q6" s="25"/>
+      <c r="R6" s="26"/>
+      <c r="S6" s="25"/>
+      <c r="T6" s="9"/>
+      <c r="U6" s="9"/>
+      <c r="V6" s="9"/>
+      <c r="W6" s="9"/>
+      <c r="X6" s="9"/>
+      <c r="Y6" s="9"/>
+      <c r="Z6" s="9"/>
+      <c r="AA6" s="9"/>
+      <c r="AB6" s="9"/>
+      <c r="AC6" s="9"/>
+      <c r="AD6" s="9"/>
+      <c r="AE6" s="9"/>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A7" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="9"/>
+      <c r="R7" s="11"/>
+      <c r="S7" s="9"/>
+      <c r="T7" s="9"/>
+      <c r="U7" s="9"/>
+      <c r="V7" s="9"/>
+      <c r="W7" s="9"/>
+      <c r="X7" s="9"/>
+      <c r="Y7" s="9"/>
+      <c r="Z7" s="9"/>
+      <c r="AA7" s="9"/>
+      <c r="AB7" s="9"/>
+      <c r="AC7" s="9"/>
+      <c r="AD7" s="9"/>
+      <c r="AE7" s="9"/>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A8" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="9"/>
+      <c r="Q8" s="9"/>
+      <c r="R8" s="11"/>
+      <c r="S8" s="9"/>
+      <c r="T8" s="9"/>
+      <c r="U8" s="9"/>
+      <c r="V8" s="9"/>
+      <c r="W8" s="9"/>
+      <c r="X8" s="9"/>
+      <c r="Y8" s="9"/>
+      <c r="Z8" s="9"/>
+      <c r="AA8" s="9"/>
+      <c r="AB8" s="9"/>
+      <c r="AC8" s="9"/>
+      <c r="AD8" s="9"/>
+      <c r="AE8" s="9"/>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="B9" s="12"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
+      <c r="N9" s="16"/>
+      <c r="O9" s="16"/>
+      <c r="P9" s="16"/>
+      <c r="Q9" s="16"/>
+      <c r="R9" s="16"/>
+      <c r="S9" s="16"/>
+      <c r="T9" s="16"/>
+      <c r="U9" s="16"/>
+      <c r="V9" s="16"/>
+      <c r="W9" s="12"/>
+      <c r="X9" s="16"/>
+      <c r="Y9" s="16"/>
+      <c r="Z9" s="16"/>
+      <c r="AA9" s="16"/>
+      <c r="AB9" s="16"/>
+      <c r="AC9" s="16"/>
+      <c r="AD9" s="16"/>
+      <c r="AE9" s="12"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C28529B-3F25-4BAF-8EFD-2BE56F93896E}">
+  <dimension ref="A1:AE9"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="9" customWidth="1"/>
+    <col min="2" max="31" width="2.875" customWidth="1"/>
+    <col min="32" max="56" width="3.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:31" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" s="6" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="3"/>
+      <c r="B2" s="13">
+        <v>1</v>
+      </c>
+      <c r="C2" s="13">
+        <v>2</v>
+      </c>
+      <c r="D2" s="13">
+        <v>3</v>
+      </c>
+      <c r="E2" s="13">
+        <v>4</v>
+      </c>
+      <c r="F2" s="13">
+        <v>5</v>
+      </c>
+      <c r="G2" s="13">
+        <v>6</v>
+      </c>
+      <c r="H2" s="13">
+        <v>7</v>
+      </c>
+      <c r="I2" s="13">
+        <v>8</v>
+      </c>
+      <c r="J2" s="13">
+        <v>9</v>
+      </c>
+      <c r="K2" s="2">
+        <v>10</v>
+      </c>
+      <c r="L2" s="2">
+        <v>11</v>
+      </c>
+      <c r="M2" s="2">
+        <v>12</v>
+      </c>
+      <c r="N2" s="2">
+        <v>13</v>
+      </c>
+      <c r="O2" s="2">
+        <v>14</v>
+      </c>
+      <c r="P2" s="2">
+        <v>15</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>16</v>
+      </c>
+      <c r="R2" s="2">
+        <v>17</v>
+      </c>
+      <c r="S2" s="2">
+        <v>18</v>
+      </c>
+      <c r="T2" s="2">
+        <v>19</v>
+      </c>
+      <c r="U2" s="2">
+        <v>20</v>
+      </c>
+      <c r="V2" s="2">
+        <v>21</v>
+      </c>
+      <c r="W2" s="2">
+        <v>22</v>
+      </c>
+      <c r="X2" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y2" s="2">
+        <v>24</v>
+      </c>
+      <c r="Z2" s="2">
+        <v>25</v>
+      </c>
+      <c r="AA2" s="2">
+        <v>26</v>
+      </c>
+      <c r="AB2" s="2">
+        <v>27</v>
+      </c>
+      <c r="AC2" s="2">
+        <v>28</v>
+      </c>
+      <c r="AD2" s="2">
+        <v>29</v>
+      </c>
+      <c r="AE2" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A3" s="7"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17"/>
+      <c r="R3" s="43"/>
+      <c r="S3" s="17"/>
+      <c r="T3" s="17"/>
+      <c r="U3" s="17"/>
+      <c r="V3" s="17"/>
+      <c r="W3" s="17"/>
+      <c r="X3" s="17"/>
+      <c r="Y3" s="17"/>
+      <c r="Z3" s="17"/>
+      <c r="AA3" s="17"/>
+      <c r="AB3" s="17"/>
+      <c r="AC3" s="17"/>
+      <c r="AD3" s="17"/>
+      <c r="AE3" s="17"/>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A4" s="7"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="S4" s="9"/>
+      <c r="T4" s="9"/>
+      <c r="U4" s="9"/>
+      <c r="V4" s="9"/>
+      <c r="W4" s="9"/>
+      <c r="X4" s="9"/>
+      <c r="Y4" s="9"/>
+      <c r="Z4" s="9"/>
+      <c r="AA4" s="9"/>
+      <c r="AB4" s="9"/>
+      <c r="AC4" s="9"/>
+      <c r="AD4" s="9"/>
+      <c r="AE4" s="9"/>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A5" s="7"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="9"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="9"/>
+      <c r="U5" s="9"/>
+      <c r="V5" s="9"/>
+      <c r="W5" s="9"/>
+      <c r="X5" s="9"/>
+      <c r="Y5" s="9"/>
+      <c r="Z5" s="9"/>
+      <c r="AA5" s="9"/>
+      <c r="AB5" s="9"/>
+      <c r="AC5" s="9"/>
+      <c r="AD5" s="9"/>
+      <c r="AE5" s="9"/>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A6" s="7"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -3203,352 +3894,6 @@
       <c r="AE8" s="9"/>
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="B9" s="12"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="16"/>
-      <c r="O9" s="16"/>
-      <c r="P9" s="16"/>
-      <c r="Q9" s="16"/>
-      <c r="R9" s="16"/>
-      <c r="S9" s="16"/>
-      <c r="T9" s="16"/>
-      <c r="U9" s="16"/>
-      <c r="V9" s="16"/>
-      <c r="W9" s="12"/>
-      <c r="X9" s="16"/>
-      <c r="Y9" s="16"/>
-      <c r="Z9" s="16"/>
-      <c r="AA9" s="16"/>
-      <c r="AB9" s="16"/>
-      <c r="AC9" s="16"/>
-      <c r="AD9" s="16"/>
-      <c r="AE9" s="12"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C28529B-3F25-4BAF-8EFD-2BE56F93896E}">
-  <dimension ref="A1:AE9"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="31" width="2.875" customWidth="1"/>
-    <col min="32" max="56" width="3.125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:31" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:31" s="6" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="3"/>
-      <c r="B2" s="13">
-        <v>1</v>
-      </c>
-      <c r="C2" s="13">
-        <v>2</v>
-      </c>
-      <c r="D2" s="13">
-        <v>3</v>
-      </c>
-      <c r="E2" s="13">
-        <v>4</v>
-      </c>
-      <c r="F2" s="13">
-        <v>5</v>
-      </c>
-      <c r="G2" s="13">
-        <v>6</v>
-      </c>
-      <c r="H2" s="13">
-        <v>7</v>
-      </c>
-      <c r="I2" s="13">
-        <v>8</v>
-      </c>
-      <c r="J2" s="13">
-        <v>9</v>
-      </c>
-      <c r="K2" s="2">
-        <v>10</v>
-      </c>
-      <c r="L2" s="2">
-        <v>11</v>
-      </c>
-      <c r="M2" s="2">
-        <v>12</v>
-      </c>
-      <c r="N2" s="2">
-        <v>13</v>
-      </c>
-      <c r="O2" s="2">
-        <v>14</v>
-      </c>
-      <c r="P2" s="2">
-        <v>15</v>
-      </c>
-      <c r="Q2" s="2">
-        <v>16</v>
-      </c>
-      <c r="R2" s="2">
-        <v>17</v>
-      </c>
-      <c r="S2" s="2">
-        <v>18</v>
-      </c>
-      <c r="T2" s="2">
-        <v>19</v>
-      </c>
-      <c r="U2" s="2">
-        <v>20</v>
-      </c>
-      <c r="V2" s="2">
-        <v>21</v>
-      </c>
-      <c r="W2" s="2">
-        <v>22</v>
-      </c>
-      <c r="X2" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y2" s="2">
-        <v>24</v>
-      </c>
-      <c r="Z2" s="2">
-        <v>25</v>
-      </c>
-      <c r="AA2" s="2">
-        <v>26</v>
-      </c>
-      <c r="AB2" s="2">
-        <v>27</v>
-      </c>
-      <c r="AC2" s="2">
-        <v>28</v>
-      </c>
-      <c r="AD2" s="2">
-        <v>29</v>
-      </c>
-      <c r="AE2" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="A3" s="7"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="11"/>
-      <c r="S3" s="9"/>
-      <c r="T3" s="9"/>
-      <c r="U3" s="9"/>
-      <c r="V3" s="9"/>
-      <c r="W3" s="9"/>
-      <c r="X3" s="9"/>
-      <c r="Y3" s="9"/>
-      <c r="Z3" s="9"/>
-      <c r="AA3" s="9"/>
-      <c r="AB3" s="9"/>
-      <c r="AC3" s="9"/>
-      <c r="AD3" s="9"/>
-      <c r="AE3" s="9"/>
-    </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="A4" s="7"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="9"/>
-      <c r="S4" s="9"/>
-      <c r="T4" s="9"/>
-      <c r="U4" s="9"/>
-      <c r="V4" s="9"/>
-      <c r="W4" s="9"/>
-      <c r="X4" s="9"/>
-      <c r="Y4" s="9"/>
-      <c r="Z4" s="9"/>
-      <c r="AA4" s="9"/>
-      <c r="AB4" s="9"/>
-      <c r="AC4" s="9"/>
-      <c r="AD4" s="9"/>
-      <c r="AE4" s="9"/>
-    </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="A5" s="7"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="9"/>
-      <c r="Q5" s="9"/>
-      <c r="R5" s="9"/>
-      <c r="S5" s="9"/>
-      <c r="T5" s="9"/>
-      <c r="U5" s="9"/>
-      <c r="V5" s="9"/>
-      <c r="W5" s="9"/>
-      <c r="X5" s="9"/>
-      <c r="Y5" s="9"/>
-      <c r="Z5" s="9"/>
-      <c r="AA5" s="9"/>
-      <c r="AB5" s="9"/>
-      <c r="AC5" s="9"/>
-      <c r="AD5" s="9"/>
-      <c r="AE5" s="9"/>
-    </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="A6" s="7"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
-      <c r="P6" s="9"/>
-      <c r="Q6" s="9"/>
-      <c r="R6" s="11"/>
-      <c r="S6" s="9"/>
-      <c r="T6" s="9"/>
-      <c r="U6" s="9"/>
-      <c r="V6" s="9"/>
-      <c r="W6" s="9"/>
-      <c r="X6" s="9"/>
-      <c r="Y6" s="9"/>
-      <c r="Z6" s="9"/>
-      <c r="AA6" s="9"/>
-      <c r="AB6" s="9"/>
-      <c r="AC6" s="9"/>
-      <c r="AD6" s="9"/>
-      <c r="AE6" s="9"/>
-    </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="A7" s="7"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="9"/>
-      <c r="O7" s="9"/>
-      <c r="P7" s="9"/>
-      <c r="Q7" s="9"/>
-      <c r="R7" s="11"/>
-      <c r="S7" s="9"/>
-      <c r="T7" s="9"/>
-      <c r="U7" s="9"/>
-      <c r="V7" s="9"/>
-      <c r="W7" s="9"/>
-      <c r="X7" s="9"/>
-      <c r="Y7" s="9"/>
-      <c r="Z7" s="9"/>
-      <c r="AA7" s="9"/>
-      <c r="AB7" s="9"/>
-      <c r="AC7" s="9"/>
-      <c r="AD7" s="9"/>
-      <c r="AE7" s="9"/>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="A8" s="7"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
-      <c r="M8" s="9"/>
-      <c r="N8" s="9"/>
-      <c r="O8" s="9"/>
-      <c r="P8" s="9"/>
-      <c r="Q8" s="9"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="9"/>
-      <c r="T8" s="9"/>
-      <c r="U8" s="9"/>
-      <c r="V8" s="9"/>
-      <c r="W8" s="9"/>
-      <c r="X8" s="9"/>
-      <c r="Y8" s="9"/>
-      <c r="Z8" s="9"/>
-      <c r="AA8" s="9"/>
-      <c r="AB8" s="9"/>
-      <c r="AC8" s="9"/>
-      <c r="AD8" s="9"/>
-      <c r="AE8" s="9"/>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.4">
       <c r="B9" s="15" t="s">
         <v>9</v>
       </c>
@@ -3702,25 +4047,27 @@
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A3" s="7"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="11"/>
-      <c r="S3" s="9"/>
-      <c r="T3" s="9"/>
+      <c r="B3" s="44" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="45"/>
+      <c r="L3" s="45"/>
+      <c r="M3" s="45"/>
+      <c r="N3" s="45"/>
+      <c r="O3" s="45"/>
+      <c r="P3" s="45"/>
+      <c r="Q3" s="45"/>
+      <c r="R3" s="46"/>
+      <c r="S3" s="45"/>
+      <c r="T3" s="45"/>
       <c r="U3" s="9"/>
       <c r="V3" s="9"/>
       <c r="W3" s="9"/>
@@ -3948,6 +4295,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="26553de7-2a3a-444c-a024-df4cb947fd03" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101005F0D9E193D28814892BA96752E68B42F" ma:contentTypeVersion="11" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="7ef2c4f7c5cf37d6221d7b1dda883374">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c" xmlns:ns3="26553de7-2a3a-444c-a024-df4cb947fd03" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="725cefcd41332f88909580cd13155635" ns2:_="" ns3:_="">
     <xsd:import namespace="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
@@ -4142,27 +4509,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="26553de7-2a3a-444c-a024-df4cb947fd03" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDC1435B-6AB6-4AB2-8181-7AB2A8D90409}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB4AC433-DB2B-4AE9-979C-606A42CB94A1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="26553de7-2a3a-444c-a024-df4cb947fd03"/>
+    <ds:schemaRef ds:uri="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{974AEB67-0EB4-422A-8375-3AEC86DF31AC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4179,23 +4545,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB4AC433-DB2B-4AE9-979C-606A42CB94A1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="26553de7-2a3a-444c-a024-df4cb947fd03"/>
-    <ds:schemaRef ds:uri="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDC1435B-6AB6-4AB2-8181-7AB2A8D90409}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>